--- a/output/pdf_financials_xlsx/AVE.xlsx
+++ b/output/pdf_financials_xlsx/AVE.xlsx
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.587955</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.925775</v>
       </c>
     </row>
     <row r="119">
@@ -2958,7 +2958,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>-0.587955</v>
       </c>

--- a/output/pdf_financials_xlsx/AVE.xlsx
+++ b/output/pdf_financials_xlsx/AVE.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.037049</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.022074</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.929298</v>
+        <v>-0.966347</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.542877</v>
+        <v>-1.564951</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.927972</v>
+        <v>-0.965021</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.541873</v>
+        <v>-1.563947</v>
       </c>
     </row>
     <row r="30">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">

--- a/output/pdf_financials_xlsx/AVE.xlsx
+++ b/output/pdf_financials_xlsx/AVE.xlsx
@@ -3040,7 +3040,11 @@
           <t>Proceeds received from flow through private placement</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>0.75285</v>
       </c>
